--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T13:22:01+00:00</t>
+    <t>2026-09-14T18:30:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T18:30:11+00:00</t>
+    <t>2026-09-15T08:39:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T08:39:16+00:00</t>
+    <t>2026-09-15T14:26:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T14:26:14+00:00</t>
+    <t>2026-09-15T15:55:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T15:55:26+00:00</t>
+    <t>2026-09-16T08:21:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T08:21:32+00:00</t>
+    <t>2026-09-16T12:46:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T12:46:48+00:00</t>
+    <t>2026-09-16T14:44:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T14:44:43+00:00</t>
+    <t>2026-09-17T07:59:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T07:59:06+00:00</t>
+    <t>2026-09-17T12:33:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T12:33:54+00:00</t>
+    <t>2026-09-18T07:05:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T07:05:38+00:00</t>
+    <t>2026-09-18T08:38:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T08:38:11+00:00</t>
+    <t>2026-09-18T11:05:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.1</t>
+    <t>0.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T11:05:21+00:00</t>
+    <t>2026-09-18T13:55:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T13:55:49+00:00</t>
+    <t>2026-09-21T11:37:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-21T11:37:47+00:00</t>
+    <t>2026-09-22T11:13:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-22T11:13:44+00:00</t>
+    <t>2026-09-23T05:33:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T05:33:05+00:00</t>
+    <t>2026-09-23T16:50:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T16:50:58+00:00</t>
+    <t>2026-09-23T17:09:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T17:09:41+00:00</t>
+    <t>2026-09-24T11:03:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-24T11:03:30+00:00</t>
+    <t>2026-09-24T15:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-24T15:40:45+00:00</t>
+    <t>2026-09-25T14:56:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-25T14:56:10+00:00</t>
+    <t>2026-09-29T10:09:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T10:09:39+00:00</t>
+    <t>2026-09-29T10:46:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T10:46:32+00:00</t>
+    <t>2026-09-29T11:13:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T11:13:32+00:00</t>
+    <t>2026-09-29T15:22:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T15:22:43+00:00</t>
+    <t>2026-09-30T17:01:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T17:01:19+00:00</t>
+    <t>2026-09-30T18:21:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T18:21:17+00:00</t>
+    <t>2026-10-01T11:37:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T11:37:05+00:00</t>
+    <t>2026-10-01T11:47:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T11:47:48+00:00</t>
+    <t>2026-10-01T21:19:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T21:19:24+00:00</t>
+    <t>2026-10-02T13:24:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1014" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1014" uniqueCount="232">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-02T13:24:17+00:00</t>
+    <t>2026-10-07T12:50:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -672,6 +672,10 @@
   </si>
   <si>
     <t>The amount of the substance.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
   </si>
   <si>
     <t>.player.quantity</t>
@@ -3509,10 +3513,10 @@
         <v>21</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>98</v>
+        <v>212</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>21</v>
@@ -3523,10 +3527,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3552,10 +3556,10 @@
         <v>182</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3606,7 +3610,7 @@
         <v>21</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>77</v>
@@ -3621,7 +3625,7 @@
         <v>98</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>21</v>
@@ -3632,10 +3636,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3741,10 +3745,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3852,10 +3856,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3965,10 +3969,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3991,13 +3995,13 @@
         <v>87</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4048,7 +4052,7 @@
         <v>21</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
@@ -4063,7 +4067,7 @@
         <v>98</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>21</v>
@@ -4074,10 +4078,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4100,13 +4104,13 @@
         <v>87</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4136,7 +4140,7 @@
         <v>171</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Z28" t="s" s="2">
         <v>173</v>
@@ -4157,7 +4161,7 @@
         <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>86</v>
@@ -4172,7 +4176,7 @@
         <v>98</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>21</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T12:50:21+00:00</t>
+    <t>2026-10-07T13:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T13:01:43+00:00</t>
+    <t>2026-10-08T06:44:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T06:44:48+00:00</t>
+    <t>2026-10-08T16:43:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T16:43:43+00:00</t>
+    <t>2026-10-08T20:06:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T20:06:16+00:00</t>
+    <t>2026-10-09T14:33:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T14:33:13+00:00</t>
+    <t>2026-10-09T16:18:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T16:18:46+00:00</t>
+    <t>2026-10-12T06:12:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T06:12:55+00:00</t>
+    <t>2026-10-12T12:45:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T12:45:08+00:00</t>
+    <t>2026-10-12T17:47:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T17:47:09+00:00</t>
+    <t>2026-10-13T16:03:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T16:03:24+00:00</t>
+    <t>2026-10-14T07:51:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T07:51:23+00:00</t>
+    <t>2026-10-14T10:33:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T10:33:13+00:00</t>
+    <t>2026-10-14T18:50:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T18:50:32+00:00</t>
+    <t>2026-10-14T21:19:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T21:19:26+00:00</t>
+    <t>2026-10-15T08:30:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T08:30:16+00:00</t>
+    <t>2026-10-15T11:48:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T11:48:20+00:00</t>
+    <t>2026-10-15T13:39:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T13:39:50+00:00</t>
+    <t>2026-10-15T16:16:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T16:16:55+00:00</t>
+    <t>2026-10-15T16:39:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-substance-wirkstoff.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T16:39:56+00:00</t>
+    <t>2026-10-16T09:51:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
